--- a/Input_Data/Phenotypic and Body Composition Data.xlsx
+++ b/Input_Data/Phenotypic and Body Composition Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\INDRANIL BISWAS\OneDrive\Desktop\Prediction_Model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anu\APT\bio\GutBiomePrediction\Input_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C491FD8-E217-4ADC-B153-2CB8A464D115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12677510-AF38-4B03-98B1-1585BE619D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -156,9 +156,6 @@
     <t>Height (cm)</t>
   </si>
   <si>
-    <t>Weight (cm)</t>
-  </si>
-  <si>
     <t>Age</t>
   </si>
   <si>
@@ -172,6 +169,9 @@
   </si>
   <si>
     <t>Subjects</t>
+  </si>
+  <si>
+    <t>Weight (Kgs)</t>
   </si>
 </sst>
 </file>
@@ -543,29 +543,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="8.7265625" style="1"/>
-    <col min="6" max="6" width="8.7265625" style="2"/>
-    <col min="7" max="7" width="15.7265625" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="5" width="8.77734375" style="1"/>
+    <col min="6" max="6" width="8.77734375" style="2"/>
+    <col min="7" max="7" width="15.77734375" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="8.77734375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" s="1" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>39</v>
@@ -577,7 +577,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -585,7 +585,7 @@
         <v>30</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D2" s="5">
         <v>167.3</v>
@@ -605,7 +605,7 @@
         <v>26.55</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -613,7 +613,7 @@
         <v>26</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="5">
         <v>155</v>
@@ -633,7 +633,7 @@
         <v>24.25</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -641,7 +641,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" s="5">
         <v>130</v>
@@ -660,7 +660,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -668,7 +668,7 @@
         <v>32</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="5">
         <v>167.3</v>
@@ -686,7 +686,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
@@ -694,7 +694,7 @@
         <v>28</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" s="5">
         <v>155.1</v>
@@ -712,7 +712,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -720,7 +720,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" s="5">
         <v>130.80000000000001</v>
@@ -738,7 +738,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
@@ -746,7 +746,7 @@
         <v>33</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="5">
         <v>167.3</v>
@@ -766,7 +766,7 @@
         <v>30.975000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -774,7 +774,7 @@
         <v>29</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" s="5">
         <v>155</v>
@@ -794,7 +794,7 @@
         <v>25.75</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -802,7 +802,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" s="5">
         <v>144.30000000000001</v>
@@ -821,7 +821,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
@@ -829,7 +829,7 @@
         <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" s="5">
         <v>158.6</v>
@@ -849,7 +849,7 @@
         <v>21.78</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -857,7 +857,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D12" s="5">
         <v>147.5</v>
@@ -876,7 +876,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
@@ -884,7 +884,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" s="5">
         <v>119.9</v>
@@ -902,7 +902,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
@@ -910,7 +910,7 @@
         <v>32</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" s="5">
         <v>158.6</v>
@@ -928,7 +928,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
@@ -936,7 +936,7 @@
         <v>28</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" s="5">
         <v>147.5</v>
@@ -954,7 +954,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
@@ -962,7 +962,7 @@
         <v>7</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" s="5">
         <v>140.30000000000001</v>
@@ -980,7 +980,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
@@ -988,7 +988,7 @@
         <v>33</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" s="5">
         <v>158.6</v>
@@ -1006,7 +1006,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>16</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>29</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D18" s="5">
         <v>147.5</v>
@@ -1032,7 +1032,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
@@ -1040,7 +1040,7 @@
         <v>8</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D19" s="5">
         <v>164.8</v>
@@ -1058,7 +1058,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>18</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>30</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D20" s="5">
         <v>168.5</v>
@@ -1086,7 +1086,7 @@
         <v>20.790000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
@@ -1094,7 +1094,7 @@
         <v>26</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D21" s="5">
         <v>146.80000000000001</v>
@@ -1114,7 +1114,7 @@
         <v>24.25</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>20</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D22" s="5">
         <v>118.2</v>
@@ -1142,7 +1142,7 @@
         <v>16.45</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>21</v>
       </c>
@@ -1150,7 +1150,7 @@
         <v>32</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D23" s="5">
         <v>168.5</v>
@@ -1168,7 +1168,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>22</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>28</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D24" s="5">
         <v>146.80000000000001</v>
@@ -1194,7 +1194,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>23</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>7</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D25" s="5">
         <v>121.5</v>
@@ -1220,7 +1220,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>24</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>33</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D26" s="5">
         <v>168.5</v>
@@ -1246,7 +1246,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>25</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>29</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D27" s="5">
         <v>146.80000000000001</v>
@@ -1272,7 +1272,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>26</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>8</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D28" s="5">
         <v>143.1</v>
@@ -1298,7 +1298,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>79</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D29" s="4">
         <v>150</v>
@@ -1324,7 +1324,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>28</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>65</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D30" s="4">
         <v>145</v>
@@ -1350,7 +1350,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>29</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>60</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D31" s="4">
         <v>142</v>
@@ -1376,7 +1376,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>30</v>
       </c>
@@ -1384,7 +1384,7 @@
         <v>68</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D32" s="4">
         <v>145</v>
@@ -1402,7 +1402,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>31</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>48</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D33" s="4">
         <v>150</v>
@@ -1428,7 +1428,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>32</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>52</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D34" s="4">
         <v>150</v>
@@ -1454,7 +1454,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>33</v>
       </c>
@@ -1462,7 +1462,7 @@
         <v>68</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D35" s="4">
         <v>135</v>
@@ -1480,7 +1480,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>34</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>66</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D36" s="4">
         <v>120</v>
@@ -1506,7 +1506,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>35</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>32</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D37" s="4">
         <v>135</v>
@@ -1532,7 +1532,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>36</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>26</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D38" s="4">
         <v>134</v>
@@ -1558,7 +1558,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>23</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D39" s="4">
         <v>123</v>
@@ -1584,7 +1584,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>38</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>6</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D40" s="4">
         <v>114</v>
